--- a/samples/ss_gndul24_ingest.xlsx
+++ b/samples/ss_gndul24_ingest.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T9"/>
+  <dimension ref="A1:U9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -536,65 +536,70 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Bus 150 kV</t>
+          <t>Bus HV</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Bus LV</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Jumlah Trafo</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Kapasitor</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Catatan Simbol</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Sirkit Bay</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Status Operasi</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Status Kerawanan</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>No Kerawanan</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Wilayah</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Sudut Pandang</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Latitude</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Longitude</t>
         </is>
@@ -633,24 +638,25 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -686,37 +692,42 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>GNDUL7</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>GNDUL</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>2</v>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
         <is>
           <t>2 IBT (unit 2,4)</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr">
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -749,30 +760,31 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
         <is>
           <t>bus section + kopel</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr">
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -807,24 +819,25 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -857,34 +870,35 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
         <is>
           <t>bus coupler</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -919,24 +933,25 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -969,30 +984,31 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
         <is>
           <t>aset milik KTT</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr">
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1025,30 +1041,31 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
         <is>
           <t>aset milik KTT</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr">
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/samples/ss_gndul24_ingest.xlsx
+++ b/samples/ss_gndul24_ingest.xlsx
@@ -687,7 +687,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2,4</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">

--- a/samples/ss_gndul24_ingest.xlsx
+++ b/samples/ss_gndul24_ingest.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U9"/>
+  <dimension ref="A1:U7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -906,12 +906,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Asari</t>
+          <t>Sambas (aset milik KTT)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ASARI</t>
+          <t>SAMBAS</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -932,7 +932,11 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>aset milik KTT</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
@@ -952,120 +956,6 @@
         </is>
       </c>
       <c r="S7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Sambas (aset milik KTT)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>SAMBAS</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Busbar GI</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>aset milik KTT</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>CSW (aset milik KTT)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>CSW</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Busbar GI</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>aset milik KTT</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1078,7 +968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1175,7 +1065,7 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SUTT Gandul - Pondok Indah</t>
+          <t>SKTT 150 kV Gandul - Pondok Indah</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1297,17 +1187,17 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SUTT Kemang - Asari</t>
+          <t>SUTT Pondok Indah - Sambas (aset milik KTT)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>KMANG</t>
+          <t>PNDAH</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ASARI</t>
+          <t>SAMBAS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1348,124 +1238,6 @@
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>SUTT Pondok Indah - Sambas (aset milik KTT)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>PNDAH</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>SAMBAS</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
-        <v>2</v>
-      </c>
-      <c r="O5" t="n">
-        <v>3</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Tidak</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>SUTT Sambas - CSW (aset milik KTT)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>SAMBAS</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>CSW</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
-      <c r="N6" t="n">
-        <v>3</v>
-      </c>
-      <c r="O6" t="n">
-        <v>4</v>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Tidak</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1478,7 +1250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1597,6 +1369,76 @@
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ASARI</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Asari</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>KMANG</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CSW</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CSW (aset milik KTT)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SAMBAS</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/samples/ss_gndul24_ingest.xlsx
+++ b/samples/ss_gndul24_ingest.xlsx
@@ -1250,7 +1250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1276,25 +1276,30 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Jenis</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Tegangan</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Sirkit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Status Operasi</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>No Kerawanan</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Sudut Pandang</t>
         </is>
@@ -1319,21 +1324,22 @@
           <t>GNDUL</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
         <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>1</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1354,21 +1360,22 @@
           <t>GNDUL</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
         <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>1</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1389,21 +1396,22 @@
           <t>KMANG</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
         <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>1</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1424,21 +1432,22 @@
           <t>SAMBAS</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
         <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>1</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1502,12 +1511,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[N-1] Arus Nominal SKTT 150 kV Gandul-Kemang masih relative kecil (634 A derating ke 500 A)</t>
+          <t>[BELUM_DITETAPKAN] Arus Nominal SKTT 150 kV Gandul-Kemang masih relative kecil (634 A derating ke 500 A)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/samples/ss_gndul24_ingest.xlsx
+++ b/samples/ss_gndul24_ingest.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U7"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -664,7 +664,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IBT 2,4 Gandul 500/150 kV</t>
+          <t>IBT 2 Gandul 500/150 kV</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2,4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -701,14 +701,10 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2 IBT (unit 2,4)</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
@@ -735,37 +731,47 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Gandul (bus 150 kV)</t>
+          <t>IBT 4 Gandul 500/150 kV</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>IBT 4 GNDUL7</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>IBT 3-Winding</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>GNDUL7</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>GNDUL</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Busbar GI</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>bus section + kopel</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
@@ -792,12 +798,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pondok Indah</t>
+          <t>Gandul (bus 150 kV)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>PNDAH</t>
+          <t>GNDUL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -806,7 +812,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -818,7 +824,11 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>bus section + kopel</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
@@ -845,12 +855,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kemang</t>
+          <t>Pondok Indah</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>KMANG</t>
+          <t>PNDAH</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -871,11 +881,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>bus coupler</t>
-        </is>
-      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
@@ -885,14 +891,10 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
@@ -906,12 +908,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sambas (aset milik KTT)</t>
+          <t>Kemang</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SAMBAS</t>
+          <t>KMANG</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -920,7 +922,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -934,7 +936,7 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>aset milik KTT</t>
+          <t>bus coupler</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -946,16 +948,77 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Sambas (aset milik KTT)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SAMBAS</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Busbar GI</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>aset milik KTT</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Milik Pelanggan</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr">
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
